--- a/source-docs/MAGIC.xlsx
+++ b/source-docs/MAGIC.xlsx
@@ -116,7 +116,7 @@
     <t>SPIN-FIRE ARMOR</t>
   </si>
   <si>
-    <t>Buffed unit deals 1D4 fire DMG back to any attackers in melee range for 3 rounds. Buffed unit makes a VIT save (10+) upon recieving buff or they suffer 1D6 fire DMG.</t>
+    <t>Buffed unit deals 1D4 fire DMG back to any attackers in melee range for 3 rounds. Buffed unit makes a VIT save (10+) upon receiving buff or they suffer 1D6 fire DMG.</t>
   </si>
   <si>
     <t>Summon a swirling barrier of fire that protects your chosen target and burns those who get too close</t>
@@ -200,1104 +200,1104 @@
     <t>Send a pulse of superheated air towards your enemies disrupting their magic defenses</t>
   </si>
   <si>
+    <t>BURN IMPURITIES</t>
+  </si>
+  <si>
+    <t>Deal 1D4 Fire DMG to yourself and cure yourself of Poison and Freeze buildup.</t>
+  </si>
+  <si>
+    <t>Summon an inner flame that burns away the toxins of the body and cures frostbite</t>
+  </si>
+  <si>
+    <t>HEAL</t>
+  </si>
+  <si>
+    <t>CONSUME FLAMES</t>
+  </si>
+  <si>
+    <t>If your target is suffering from the burned status effect cure it and heal them and yourself for 1D4 HP.</t>
+  </si>
+  <si>
+    <t>Seize control of a flame being used against you and empower yourself with its essence</t>
+  </si>
+  <si>
+    <t>SELF/ALLY (MELEE)</t>
+  </si>
+  <si>
+    <t>FORGE-FIRE</t>
+  </si>
+  <si>
+    <t>Deals an additional pt. of direct DMG per 1 pt. of equipped ARM your target has.</t>
+  </si>
+  <si>
+    <t>Engulf your target in a molten flame that heats metal and flesh like a blacksmith's forge</t>
+  </si>
+  <si>
+    <t>3 TILES</t>
+  </si>
+  <si>
+    <t>SURGING FLAME</t>
+  </si>
+  <si>
+    <t>Increase the Cast Requirement by up to 4 pts. Adding 2 fire DMG to this spell per pt. increase. The additions must be called before the cast is rolled.</t>
+  </si>
+  <si>
+    <t>Cradle this flame and charge it with your own magic power allowing it to grow in strength as well as instability</t>
+  </si>
+  <si>
+    <t>1D8 (+)</t>
+  </si>
+  <si>
+    <t>3 TILES (WIDTH)</t>
+  </si>
+  <si>
+    <t>[ ADVANCED LEVEL : 2 SPELL MEMORY TO LEARN ]</t>
+  </si>
+  <si>
+    <t>GREATER STAR FIRE</t>
+  </si>
+  <si>
+    <t>Deals 1D8 fire DMG to units within 1 tile of target area as well; Can deal 1D8 fire DMG to yourself to lower the Cast Cost to 6 (can be called during the spellcast).</t>
+  </si>
+  <si>
+    <t>Conjure a destructive missile of flame at your fingertips and fling it towards an enemy</t>
+  </si>
+  <si>
+    <t>2D8+SRV</t>
+  </si>
+  <si>
+    <t>NOXIOUS FLAME</t>
+  </si>
+  <si>
+    <t>Target must succeed a SPD save (16+) or suffer an additional 1D8 Toxic DMG</t>
+  </si>
+  <si>
+    <t>Conjure a foul flame that burns bright green with unnatural toxins</t>
+  </si>
+  <si>
+    <t>1D10+SRV</t>
+  </si>
+  <si>
+    <t>FIRE (TOXIC)</t>
+  </si>
+  <si>
+    <t>3+ACC</t>
+  </si>
+  <si>
+    <t>INFERNO</t>
+  </si>
+  <si>
+    <t>Cause the Inferno weather effect to appear within the area of the battlefield for 1D4+SRV rounds (see combat doc. for weather effects).</t>
+  </si>
+  <si>
+    <t>Blanket the area in an atmosphere so hot it ignites foliage and evaporates nearby water</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>COMET DASH</t>
+  </si>
+  <si>
+    <t>Teleport to a new tile 5 tiles away in a line. Deals DMG to all targets within linear range; targets can avoid DMG with a SPD save (18+).</t>
+  </si>
+  <si>
+    <t>Surround yourself with flames and jettison yourself forward scorching everything in your blazing path</t>
+  </si>
+  <si>
+    <t>4 TILES (LINEAR)</t>
+  </si>
+  <si>
+    <t>MAGMA MISSILE</t>
+  </si>
+  <si>
+    <t>Lower target's Fire resistance to 0 after this spell's DMG is dealt (unless they are fully immune). Lasts 1+SRV rounds.</t>
+  </si>
+  <si>
+    <t>Blast an opponent with a sizzling bolt of molten gel that leaves their defenses melted</t>
+  </si>
+  <si>
+    <t>WHITE FLAME</t>
+  </si>
+  <si>
+    <t>Revive a dead party member to 1 HP. Can deal 1D10 Fire DMG to self to lower the cast cost to 6.</t>
+  </si>
+  <si>
+    <t>Summon a wisp of the White Flame of Iridess to guide a wayward spirit back to its body</t>
+  </si>
+  <si>
+    <t>FLAME OF THE DEATHBLIGHT</t>
+  </si>
+  <si>
+    <t>Deals an additional 2D6 Mind DMG unless the target makes a successful MEM save (12+).</t>
+  </si>
+  <si>
+    <t>Call upon the soul-scorching fires controlled by the God of the Corrupted Dead, Mhire</t>
+  </si>
+  <si>
+    <t>FIRE (MIND)</t>
+  </si>
+  <si>
+    <t>2+VIT TILES</t>
+  </si>
+  <si>
+    <t>DAWN'S BLAZE</t>
+  </si>
+  <si>
+    <t>Deals an additional HD10 Fire DMG if the target is at their maximum HP.</t>
+  </si>
+  <si>
+    <t>Cast a bright flame that burns stronger as a first-strike like the first rays of the sun at dawn</t>
+  </si>
+  <si>
+    <t>BURNING EARTH</t>
+  </si>
+  <si>
+    <t>Create up to 3 Fire Tiles within the designated range. If a unit is standing on one of these tiles they can make a SPD save (13+) to jump to an adjacent tile.</t>
+  </si>
+  <si>
+    <t>Ignite the very ground you walk upon to trap your foes in a great burning blaze</t>
+  </si>
+  <si>
+    <t>1 TILE (X3)</t>
+  </si>
+  <si>
+    <t>MELTDOWN</t>
+  </si>
+  <si>
+    <t>Deals an additional HD10 direct DMG to targets with a Fire weakness at the expense of dealing 1D6 Direct DMG to yourself.</t>
+  </si>
+  <si>
+    <t>Sacrifice your own vitality as fuel to conjure a devastating blaze that burns beyond physical abjuration.</t>
+  </si>
+  <si>
+    <t>[ MASTER LEVEL : 3 SPELL MEMORY TO LEARN ]</t>
+  </si>
+  <si>
+    <t>GRAND STAR FIRE</t>
+  </si>
+  <si>
+    <t>Deals 1D10 fire DMG to units within 1 tile of target area as well; Can deal 1D10 fire DMG to yourself to lower the Cast Cost to 6 (can be called during the spellcast).</t>
+  </si>
+  <si>
+    <t>Fire a screeching bolt of white-hot flame out of the hands that impacts your victim like a burning meteorite</t>
+  </si>
+  <si>
+    <t>3D8+SRV</t>
+  </si>
+  <si>
+    <t>PYROCLASTIC LIGHTNING</t>
+  </si>
+  <si>
+    <t>Targets within a 3x3 area of the main target make a SPD save (20+) or suffer 2D10 Electric DMG</t>
+  </si>
+  <si>
+    <t>Create an explosion of flame so powerful that it causes red arcs of volcanic lightning to appear</t>
+  </si>
+  <si>
+    <t>2D10+SRV</t>
+  </si>
+  <si>
+    <t>FIRE (ELECTRIC)</t>
+  </si>
+  <si>
+    <t>1 TARGET (3X3 AREA)</t>
+  </si>
+  <si>
+    <t>NOVA</t>
+  </si>
+  <si>
+    <t>Deals DMG to all in range / area. Destroys any destructible objects, tiles or obstacles in area.</t>
+  </si>
+  <si>
+    <t>Decimate a large area of the battlefield with a scorching explosion</t>
+  </si>
+  <si>
+    <t>10 TILES</t>
+  </si>
+  <si>
+    <t>5X5 AREA</t>
+  </si>
+  <si>
+    <t>FUNERAL PYRE</t>
+  </si>
+  <si>
+    <t>Can only be cast right when you are brought to 0 HP; This spell can not be charged. Deal DMG to all enemy units within a 5x5 area and add 1D6 to your Fate Roll.</t>
+  </si>
+  <si>
+    <t>(3D6+SRV)</t>
+  </si>
+  <si>
+    <t>METEORITE</t>
+  </si>
+  <si>
+    <t>Additionally takes 1 Stamina to cast; This spell can harm allied units regardless of defensive skills or other measures. Destroys all breakable objects/tiles in area.</t>
+  </si>
+  <si>
+    <t>5D10+SRV</t>
+  </si>
+  <si>
+    <t>30 TILES</t>
+  </si>
+  <si>
+    <t>SUNLIGHT BEAM</t>
+  </si>
+  <si>
+    <t>Deals DMG to all in the area; Deals an additional 1D8 Light DMG unless target(s) make a STR save (18+).</t>
+  </si>
+  <si>
+    <t>FIRE (LIGHT)</t>
+  </si>
+  <si>
+    <t>10 TILES (LINEAR)</t>
+  </si>
+  <si>
+    <t>FIRES OF CREATION</t>
+  </si>
+  <si>
+    <t>Perform an Armorer action using gear / materials you have on hand without having to rest or camp.</t>
+  </si>
+  <si>
+    <t>OCEAN'S CALL ARCANA</t>
+  </si>
+  <si>
+    <t>GEYSER</t>
+  </si>
+  <si>
+    <t>Units within the 3x3 Area around the initial geyser must make a SPD save (15+) or they take 1D6 water DMG. Create water tiles on unoccupied tiles within 3x3 area.</t>
+  </si>
+  <si>
+    <t>Cause an eruption of water to breach the ground splashing an area with destructive force</t>
+  </si>
+  <si>
+    <t>1D8+VIT</t>
+  </si>
+  <si>
+    <t>WATER</t>
+  </si>
+  <si>
+    <t>FROST MISSILE</t>
+  </si>
+  <si>
+    <t>Reduce target's MOVE by 1 for 2 rounds (effect can stack up to 3 times).</t>
+  </si>
+  <si>
+    <t>Launch an icy projectile from your hands that bursts into a biting blast of frost when it finds its mark</t>
+  </si>
+  <si>
+    <t>ICE</t>
+  </si>
+  <si>
+    <t>ARMOR OF WINTER</t>
+  </si>
+  <si>
+    <t>Grants +2 ARM. ARM is reduced by 1 each time the buffed unit is hit. Fire / Crush DMG removes this buff completely.</t>
+  </si>
+  <si>
+    <t>Solidify plates of ice around the body granting a temporary but sturdy bit of defense</t>
+  </si>
+  <si>
+    <t>WATER VEIL</t>
+  </si>
+  <si>
+    <t>Grants +1 BAR and Water / Ice resistance (1) for the next 1+VIT rounds.</t>
+  </si>
+  <si>
+    <t>Create a cloak of glowing water that filters magical energy and absorbs cold</t>
+  </si>
+  <si>
+    <t>ICE BLADE</t>
+  </si>
+  <si>
+    <t>Blade is treated like an equipped weapon (replaces channeling item). Has the stats of the spell effect. Lasts 1D4+VIT rounds. Can be used in the same action when summoned.</t>
+  </si>
+  <si>
+    <t>Form a deadly-sharp blade of ice over your staff or wand and wield it like a crude scimitar</t>
+  </si>
+  <si>
+    <t>1D6+VIT</t>
+  </si>
+  <si>
+    <t>SLASH +ICE</t>
+  </si>
+  <si>
+    <t>GLACIATE</t>
+  </si>
+  <si>
+    <t>Create Ice Tiles within the chosen 2x2 Area.</t>
+  </si>
+  <si>
+    <t>Freeze a small patch of ground nearby to obstruct foes or quell flames</t>
+  </si>
+  <si>
+    <t>5 TILES</t>
+  </si>
+  <si>
+    <t>2X2 AREA</t>
+  </si>
+  <si>
+    <t>ICE PILLAR</t>
+  </si>
+  <si>
+    <t>Create a pillar of ice equal to 1 lv. of elevation; Can be created on a unit's tile. Pillar has 12 HP, Fire / Crush weak (2), Water/Ice/Pierce resist (2).</t>
+  </si>
+  <si>
+    <t>Raise a column of hard-packed ice to reach greater heights or better defend and area</t>
+  </si>
+  <si>
+    <t>5+VIT TILES</t>
+  </si>
+  <si>
+    <t>1 TILE</t>
+  </si>
+  <si>
+    <t>PRESSURE BUBBLE</t>
+  </si>
+  <si>
+    <t>Target takes an additional 1D6 Crush DMG unless they succeed a VIT save (12+). Create a water tile on targeted space.</t>
+  </si>
+  <si>
+    <t>Form a bubble filled with the pressure of the ocean depths and burst it, unleashing a rippling pulse</t>
+  </si>
+  <si>
+    <t>WATER (CRUSH)</t>
+  </si>
+  <si>
+    <t>WATER WHIP</t>
+  </si>
+  <si>
+    <t>Create a water tile on the targeted space. Target must make a SPD save (10+) or their STR is lowered by 1 for 2 rounds.</t>
+  </si>
+  <si>
+    <t>Draw water from the air around you and form it into a painful whip</t>
+  </si>
+  <si>
+    <t>2 TILE MELEE</t>
+  </si>
+  <si>
+    <t>CASCADE</t>
+  </si>
+  <si>
+    <t>Deals DMG to all units in range; Units that take DMG must also make a SPD save (14+) or get knocked back in the direction of the attack 2 tiles.</t>
+  </si>
+  <si>
+    <t>Summon a forceful stream of water that crashes into foes like a rushing river</t>
+  </si>
+  <si>
+    <t>5 TILES (LINEAR)</t>
+  </si>
+  <si>
+    <t>1 TILE (LINEAR)</t>
+  </si>
+  <si>
+    <t>CLEAR SKIES</t>
+  </si>
+  <si>
+    <t>End any active weather effect within the battlefield area. If this weather is a persistent part of the area/dungeon it returns in 1D4+VIT rounds.</t>
+  </si>
+  <si>
+    <t>Send a magic wave skyward that dispels turbulent weather clearing the skies above you</t>
+  </si>
+  <si>
+    <t>DOUSE</t>
+  </si>
+  <si>
+    <t>Cure the target of the burned status. Grant your target Fire resist (1) and electric weakness (1). Lasts 2 rounds.</t>
+  </si>
+  <si>
+    <t>Conjure a small rain cloud above your target bathing them in water</t>
+  </si>
+  <si>
+    <t>HEAL / DEBUFF</t>
+  </si>
+  <si>
+    <t>HYDRATION</t>
+  </si>
+  <si>
+    <t>Restore 1D6 HP to all allied units within 2 spaces of a water tile or to all allies if the Rain weather effect is active.</t>
+  </si>
+  <si>
+    <t>Absorb the healing waters touching the skin like a thirsting flower</t>
+  </si>
+  <si>
+    <t>SELF/ALLY</t>
+  </si>
+  <si>
+    <t>(ALL)</t>
+  </si>
+  <si>
+    <t>RAINFALL</t>
+  </si>
+  <si>
+    <t>Cause the Rain weather effect to appear within the area of the battlefield for 1D4+VIT rounds (see combat doc. for weather effects).</t>
+  </si>
+  <si>
+    <t>Create your own miniature rain storm, forming gray clouds above your area</t>
+  </si>
+  <si>
+    <t>FROST TOMB</t>
+  </si>
+  <si>
+    <t>Target suffers 1D4 pts. of the Freeze status buildup.</t>
+  </si>
+  <si>
+    <t>Freeze the air around an enemy encasing them in a tomb of ice</t>
+  </si>
+  <si>
+    <t>2D6+VIT</t>
+  </si>
+  <si>
+    <t>3+VIT TILES</t>
+  </si>
+  <si>
+    <t>GLACIAL LANCE</t>
+  </si>
+  <si>
+    <t>Pierce DMG ignores target's Pierce resistance by 1 level ; Deals an additional 1D6 Ice DMG if this spell was cast in 1 turn.</t>
+  </si>
+  <si>
+    <t>Form a spear of lethally sharp ice and launch it at your opponent, rending them and chilling them simultaneously</t>
+  </si>
+  <si>
+    <t>1D10+VIT</t>
+  </si>
+  <si>
+    <t>PIERCE (ICE)</t>
+  </si>
+  <si>
+    <t>TIDAL SWEEP</t>
+  </si>
+  <si>
+    <t>Damages all within the area (spell is always centered on the caster).</t>
+  </si>
+  <si>
+    <t>Summon a great wave that crushes all within its breadth</t>
+  </si>
+  <si>
+    <t>2D8+VIT</t>
+  </si>
+  <si>
+    <t>5 TILES (WIDTH)</t>
+  </si>
+  <si>
+    <t>SHARD STORM</t>
+  </si>
+  <si>
+    <t>Target(s) must make a VIT save (17+) or suffer the Needled status effect.</t>
+  </si>
+  <si>
+    <t>Crystalize and freeze the air above your enemies causing needles of solid ice to fall upon them</t>
+  </si>
+  <si>
+    <t>3D4+VIT</t>
+  </si>
+  <si>
+    <t>4+VIT TILES</t>
+  </si>
+  <si>
+    <t>FLOOD</t>
+  </si>
+  <si>
+    <t>Deals DMG to all enemy units- Does not harm allied units; Destroys all fire tiles in the area.</t>
+  </si>
+  <si>
+    <t>Conjure the power of violent floodwaters sweeping away your enemies while gently passing over your allies</t>
+  </si>
+  <si>
+    <t>WATER FORM</t>
+  </si>
+  <si>
+    <t>Melt into a puddle of water; You can move to any connected water tiles freely. You are immune to all DMG but Electric in this form (lasts 2 rounds or until ended by caster).</t>
+  </si>
+  <si>
+    <t>Transmute your body into liquid water allowing you to meld with other sources and avoid detection</t>
+  </si>
+  <si>
+    <t>GREAT GEYSER</t>
+  </si>
+  <si>
+    <t>Units within the 3x3 Area around the initial geyser must make a SPD save (16+) or they take 1D8 water DMG.</t>
+  </si>
+  <si>
+    <t>Cause a massive eruption of water to breach the ground splashing an area with destructive force</t>
+  </si>
+  <si>
+    <t>FREEZE</t>
+  </si>
+  <si>
+    <t>Target suffers 2D4 pts. of the Freeze status buildup.</t>
+  </si>
+  <si>
+    <t>Grasp your target, freezing them with a magic chill</t>
+  </si>
+  <si>
+    <t>STATUS EFFECT</t>
+  </si>
+  <si>
+    <t>COMPACTION</t>
+  </si>
+  <si>
+    <t>Deals DMG to all enemy units suffering from any Freeze buildup; Fully frozen targets take an additional 1D6 DMG. This ends the target's freeze buildup/effect.</t>
+  </si>
+  <si>
+    <t>Reach out and take control of the frost covering your freezing prey and clamp the elemental ice down upon them</t>
+  </si>
+  <si>
+    <t>(3D6+VIT)</t>
+  </si>
+  <si>
+    <t>CRUSH</t>
+  </si>
+  <si>
+    <t>(?)</t>
+  </si>
+  <si>
+    <t>SPELL NAME</t>
+  </si>
+  <si>
+    <t>GREAT STORM ARTS</t>
+  </si>
+  <si>
+    <t>SHOCKING DART</t>
+  </si>
+  <si>
+    <t>Fire a small bolt of electricity that travels through the air and finds its mark near-instantly</t>
+  </si>
+  <si>
+    <t>1D4+SPD</t>
+  </si>
+  <si>
+    <t>ELECTRIC</t>
+  </si>
+  <si>
+    <t>12 TILES</t>
+  </si>
+  <si>
+    <t>AIR BLAST</t>
+  </si>
+  <si>
+    <t>Targets within area who do not fully resist this spells' DMG are knocked back 1D4 tiles.</t>
+  </si>
+  <si>
+    <t>Call forth a powerful wind that sends everything in front of you reeling backward</t>
+  </si>
+  <si>
+    <t>1D6+SPD</t>
+  </si>
+  <si>
+    <t>WIND</t>
+  </si>
+  <si>
+    <t>VENTILATION</t>
+  </si>
+  <si>
+    <t>Clear the battlefield of smoke, fog, poison mist, or any other gaseous substance that linger on the battlefield.</t>
+  </si>
+  <si>
+    <t>Summon a sweeping gust of wind that encircles the area cleansing it of smoke and dust</t>
+  </si>
+  <si>
+    <t>FRESH AIR</t>
+  </si>
+  <si>
+    <t>Restore 1D4 HP and cleanse the target of any coated substances (water, oil, etc.)</t>
+  </si>
+  <si>
+    <t>Call a soothing magic wind to restore vitality and loose foreign substances from the body</t>
+  </si>
+  <si>
+    <t>SELF/ALLY (5 TILES)</t>
+  </si>
+  <si>
+    <t>THUNDER ECHO</t>
+  </si>
+  <si>
+    <t>Targets within area also take 1D6 Sound DMG unless they succeed a VIT save (13+).</t>
+  </si>
+  <si>
+    <t>Call down a miniature bolt of lightning followed by a booming echo of thunder</t>
+  </si>
+  <si>
+    <t>ELECTRIC (SOUND)</t>
+  </si>
+  <si>
+    <t>ZEPHYR</t>
+  </si>
+  <si>
+    <t>Destroys fire tiles within a 3x3 area of your target.</t>
+  </si>
+  <si>
+    <t>Surround an enemy in a violent spiral of cutting wind</t>
+  </si>
+  <si>
+    <t>ELECTROCUTE</t>
+  </si>
+  <si>
+    <t>Target must also make a VIT save (11+) or drop their equipped weapon(s).</t>
+  </si>
+  <si>
+    <t>Grasp your quarry with hands charged with crackling blue electricity</t>
+  </si>
+  <si>
+    <t>1D8+SPD</t>
+  </si>
+  <si>
+    <t>CLOUD LEAP</t>
+  </si>
+  <si>
+    <t>Gain fall DMG immunity. Target's jump distance is buffed to 4+STR tiles and 2 levels of elevation. Lasts 1D4+SPD rounds.</t>
+  </si>
+  <si>
+    <t>Summon an enchanted wind to carry your jumps further and protect you from plummeting</t>
+  </si>
+  <si>
+    <t>SELF/ALLY (7 TILES)</t>
+  </si>
+  <si>
+    <t>BLUSTER CLOAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranged weapon ATKs (that deal pierce, slash or crush DMG) have disadvantage against the buffed target. Lasts 1D4 rounds.  </t>
+  </si>
+  <si>
+    <t>Wreathe yourself in swirling winds that deflect incoming projectiles</t>
+  </si>
+  <si>
+    <t>ENERGIZE</t>
+  </si>
+  <si>
+    <t>Increase target's MOVE and EVA by 1 for 1+ (target's) SPD rounds.</t>
+  </si>
+  <si>
+    <t>Charge your muscles with magical electric impulses that aid in reaction and speed</t>
+  </si>
+  <si>
+    <t>ARCING SHIELD</t>
+  </si>
+  <si>
+    <t>When melee DMG / a Martial Maneuver is dealt to the buffed unit deal 1D6 elec. DMG back to the attacker (attacker can evade with SPD 15+). Lasts 3 rounds.</t>
+  </si>
+  <si>
+    <t>Temporarily enchant an equipped garb with a magic charge able to retaliate with shocks toward an attacker</t>
+  </si>
+  <si>
+    <t>(ELEC)</t>
+  </si>
+  <si>
+    <t>THUNDER FIST</t>
+  </si>
+  <si>
+    <t>Target must make a VIT save (13+) or become staggered for 1 round.</t>
+  </si>
+  <si>
+    <t>Release a booming ripple of thunder from a closed, concentrated fist</t>
+  </si>
+  <si>
+    <t>SOUND</t>
+  </si>
+  <si>
+    <t>SPLITTING BOLT</t>
+  </si>
+  <si>
+    <t>Spell can hit up to 3 targets; Only 1 target per projectile.</t>
+  </si>
+  <si>
+    <t>Fire sparks of electricity that split into three arcs that chase their targets with ferocity</t>
+  </si>
+  <si>
+    <t>ELEC</t>
+  </si>
+  <si>
+    <t>3+SPD TILES</t>
+  </si>
+  <si>
+    <t>LIGHTNING BOLT</t>
+  </si>
+  <si>
+    <t>DMG ignores BAR and can not miss unless the target is fully immune to spell DMG / electric DMG in some way.</t>
+  </si>
+  <si>
+    <t>Call down a devastating bolt of lightning on your enemy striking them with the elemental ferocity of nature herself</t>
+  </si>
+  <si>
+    <t>2D10+SPD</t>
+  </si>
+  <si>
+    <t>ELECTRIFICATION CIRCLE</t>
+  </si>
+  <si>
+    <t>Allied units standing within circle add 1D6 electric DMG to any ATKs / spells used. Lasts 2+(caster's)SPD rounds.</t>
+  </si>
+  <si>
+    <t>Summon a magic circle of lightning that infuses spells, arrows and blades with the power of the storm</t>
+  </si>
+  <si>
+    <t>(ELECTRIC)</t>
+  </si>
+  <si>
+    <t>DOWNDRAFT</t>
+  </si>
+  <si>
+    <t>Launch yourself into the air avoiding enemies and tiles on the ground; Land safely on a space up to 5 tiles away (elevation adds +1 move distance)</t>
+  </si>
+  <si>
+    <t>Expel a blast of air downward launching yourself into the sky and away from danger</t>
+  </si>
+  <si>
+    <t>2D6+SPD</t>
+  </si>
+  <si>
+    <t>BOLT JUMP</t>
+  </si>
+  <si>
+    <t>Teleport to a space within 10 tiles. Deal 1D6+SPD Electric DMG to any targets within 1 tile of your chosen warp point.</t>
+  </si>
+  <si>
+    <t>Convert your body into pure electricity and jump to a distant space</t>
+  </si>
+  <si>
+    <t>(1D6+SPD)</t>
+  </si>
+  <si>
+    <t>(1 TILE RADIUS)</t>
+  </si>
+  <si>
+    <t>ARCING BOLT</t>
+  </si>
+  <si>
+    <t>Deals DMG to all in range / area.</t>
+  </si>
+  <si>
+    <t>Cast out a flurry of dancing electric bolts that fan out in a wide area of destruction</t>
+  </si>
+  <si>
+    <t>2D8+SPD</t>
+  </si>
+  <si>
+    <t>3 TILES (LINEAR)</t>
+  </si>
+  <si>
+    <t>LIGHTNING STORM</t>
+  </si>
+  <si>
+    <t>Cause the Lightning Storm weather effect to appear within the area of the battlefield for 1D4+SPD rounds (see combat doc. for weather effects).</t>
+  </si>
+  <si>
+    <t>Summon a localized storm of elemental lightning, dangerous and untamable</t>
+  </si>
+  <si>
+    <t>LIGHTNING ROD</t>
+  </si>
+  <si>
+    <t>Target is struck by the next lightning bolt that occurs during the Lightning Storm weather effect (effect ends after target is struck).</t>
+  </si>
+  <si>
+    <t>Mark your target with an invisible thread connecting them to the electricity in the sky above</t>
+  </si>
+  <si>
+    <t>CONDUCTIVE AURA</t>
+  </si>
+  <si>
+    <t>Draw any electric DMG being dealt by enemy units towards yourself and gain Electric resistance (2). Lasts 2+INT rounds.</t>
+  </si>
+  <si>
+    <t>Cast a force around you that conducts all electricity on the battlefield</t>
+  </si>
+  <si>
+    <t>DERECHO</t>
+  </si>
+  <si>
+    <t>Summon a vortex of crushing winds that decimates all enemies and spares friendly combatants</t>
+  </si>
+  <si>
+    <t>1D10+SPD</t>
+  </si>
+  <si>
+    <t>GALE CIRCLE</t>
+  </si>
+  <si>
+    <t>Can be cast on an unoccupied tile as a trap (sprung when tile walked over). Target must also make a SPD save (17+) or become Staggered.</t>
+  </si>
+  <si>
+    <t>Create a swirl of wind on the ground that contains the power of a small tornado waiting to spring forth</t>
+  </si>
+  <si>
+    <t>7 TILES (SPAWN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>LIGHTNING BEAM</t>
+  </si>
+  <si>
+    <t>Beam damages all within the 6 tile line. Can be cast through objects / other units.</t>
+  </si>
+  <si>
+    <t>Fire a deadly ray of electricity from your palms that shoots right through everything in its way</t>
+  </si>
+  <si>
+    <t>6 TILES (LINEAR)</t>
+  </si>
+  <si>
+    <t>CYCLONE</t>
+  </si>
+  <si>
+    <t>7D6+SPD</t>
+  </si>
+  <si>
+    <t>6X6 AREA</t>
+  </si>
+  <si>
+    <t>ARCANE CHARGE</t>
+  </si>
+  <si>
+    <t>Return 1D4 pts. of charge to a magic item within range.</t>
+  </si>
+  <si>
+    <t>CHAIN LIGHTNING</t>
+  </si>
+  <si>
+    <t>1 DMG roll is made; Deals DMG to any other enemy units within 3 tiles of the original target unit.</t>
+  </si>
+  <si>
+    <t>2D12+SPD</t>
+  </si>
+  <si>
+    <t>1 (+) TARGET(S)</t>
+  </si>
+  <si>
+    <t>ACCELERATION</t>
+  </si>
+  <si>
+    <t>Grants target an additional slot in the turn order; A new Initiative roll is made for this slot (extra turn is removed from turn order after 2 rounds).</t>
+  </si>
+  <si>
+    <t>HEART SHOCK</t>
+  </si>
+  <si>
+    <t>Revive a KO'd or dead ally to 1 HP.</t>
+  </si>
+  <si>
+    <t>ALLY (MELEE)</t>
+  </si>
+  <si>
+    <t>CRASH BOLT</t>
+  </si>
+  <si>
+    <t>Target also becomes staggered unless they succeed a VIT save (20+).</t>
+  </si>
+  <si>
+    <t>Catch a falling bolt of lightning and form it into a condensed ball of explosive electric energy</t>
+  </si>
+  <si>
+    <t>8 TILES</t>
+  </si>
+  <si>
+    <t>ARCADIAN ARTS</t>
+  </si>
+  <si>
+    <t>SPLINTER STONE</t>
+  </si>
+  <si>
+    <t>Target(s) must make a SPD save (11+) or suffer the Needled status effect.</t>
+  </si>
+  <si>
+    <t>Acquire a nearby rock, brick or other mineral material and cause it to explode into sharp shards</t>
+  </si>
+  <si>
+    <t>PIERCE</t>
+  </si>
+  <si>
+    <t>TANGLE VINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase Cast Cost by 2 to add another target that is within range (up to 3 targets). Immobilize target(s) until they make a STR check of 10+ on their turn. </t>
+  </si>
+  <si>
+    <t>Call spiraling vines to sprout from below that grasp at anything they touch</t>
+  </si>
+  <si>
+    <t>5+SRV TILES</t>
+  </si>
+  <si>
+    <t>1-? TARGETS</t>
+  </si>
+  <si>
+    <t>OIL STREAM</t>
+  </si>
+  <si>
+    <t>Covers the target in oil granting fire weakness (1) for 2 rounds unless the target succeeds a SPD save (12+).</t>
+  </si>
+  <si>
+    <t>Cause a small eruption of oil to burst from below an enemy coating them in flammable black tar.</t>
+  </si>
+  <si>
+    <t>SWARM</t>
+  </si>
+  <si>
+    <t>At the end of the caster's turn deals 1D4+SRV Toxic DMG or moves to closest enemy unit after initial target dies. Lasts 1D4 rounds.</t>
+  </si>
+  <si>
+    <t>Call a cloud of biting insects to your aid that tenaciously swarms your enemies</t>
+  </si>
+  <si>
+    <t>SUMMON</t>
+  </si>
+  <si>
+    <t>TOXIC</t>
+  </si>
+  <si>
+    <t>3 TILES (SPAWN)</t>
+  </si>
+  <si>
+    <t>1 TARGET (AT A TIME)</t>
+  </si>
+  <si>
+    <t>ROCK LAUNCH</t>
+  </si>
+  <si>
+    <t>Target must also make a VIT save (14+) or suffer the Staggered status effect.</t>
+  </si>
+  <si>
+    <t>Tear a chunk of earth out of the ground and launch it at a foe with magic-enhanced strength</t>
+  </si>
+  <si>
+    <t>2+STR TILES</t>
+  </si>
+  <si>
+    <t>STINGER TRAP</t>
+  </si>
+  <si>
+    <t>Can be cast on an unoccupied tile as a trap (sprung when tile walked over). Target must also make a SPD save (12+) or their turn immediately ends and they become Poisoned.</t>
+  </si>
+  <si>
+    <t>Compel a swarm of scorpions to ambush your enemies, piercing them with venom-filled stingers</t>
+  </si>
+  <si>
+    <t>1D4+SRV</t>
+  </si>
+  <si>
+    <t>8 TILES (SPAWN)</t>
+  </si>
+  <si>
+    <t>LEAF CUTTER</t>
+  </si>
+  <si>
+    <t>This spell ignores 1 level of the target's Slash resistance</t>
+  </si>
+  <si>
+    <t>Momentarily transform a simple leaf or flower petal into a razor-sharp blade</t>
+  </si>
+  <si>
+    <t>SLASH</t>
+  </si>
+  <si>
+    <t>ACID DART</t>
+  </si>
+  <si>
+    <t>Deals an additional 1D6 toxic DMG to targets with a BAR value of 0.</t>
+  </si>
+  <si>
+    <t>Form an arrow of bubbling green acid in your hand and fire it towards an enemy</t>
+  </si>
+  <si>
+    <t>FORAGER'S FRIEND</t>
+  </si>
+  <si>
+    <t>Can only be cast at camp (uses camp action); Create edible plants that restore 1D4 Stamina to the party.</t>
+  </si>
+  <si>
+    <t>Grow a bushel of hardy, nutritious vegetables to help keep your party fed</t>
+  </si>
+  <si>
+    <t>THORN WOOD</t>
+  </si>
+  <si>
+    <t>Cast on a target's weapon has wood as it's material type grant it +1D4 toxic DMG and a buff that poisons those struck with it (target can save from poison effect with VIT 12+). Lasts 1D4+SRV rounds.</t>
+  </si>
+  <si>
+    <t>Coax venomous thorns to sprout from the wood of your weapons, granting them poisonous properties</t>
+  </si>
+  <si>
+    <t>(TOXIC)</t>
+  </si>
+  <si>
+    <t>BRITTLE BEAM</t>
+  </si>
+  <si>
+    <t>Lowers target's Crush and Pierce resistance by 1 level for 2 rounds if they took DMG from this spell (does not cause Crush/Pierce weakness).</t>
+  </si>
+  <si>
+    <t>Fire an acidic-green ray that melts small holes in hide and armor</t>
+  </si>
+  <si>
+    <t>CALM ELEMENTS</t>
+  </si>
+  <si>
+    <t>Cure a target of the burned and frozen statuses.</t>
+  </si>
+  <si>
+    <t>Dispel harmful elemental effects from the body, returning their energies to nature</t>
+  </si>
+  <si>
+    <t>VULNERARY</t>
+  </si>
+  <si>
+    <t>Allied units can consume a plant using an instant action to heal 1D4+(caster's) SRV HP. (1+SRV healing plants spawn upon casting).</t>
+  </si>
+  <si>
+    <t>Call forth a bushel of magical healing herbs from the ground that magically restore your party's vitality</t>
+  </si>
+  <si>
+    <t>EARTHEN ARMOR</t>
+  </si>
+  <si>
+    <t>Gain +3 temporary ARM; Lowers your EVA by 3 as well. Each time you are hit lower both of these effects by 1.</t>
+  </si>
+  <si>
+    <t>Form protective plates of stone across the body that protect the body from physical harm</t>
+  </si>
+  <si>
+    <t>CROW CALL</t>
+  </si>
+  <si>
+    <t>Targets take no DMG from this spell if they have any Lv. of Pierce resistance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call upon a flock of night-black crows to assault a group of your enemies with sharp beaks and talons </t>
+  </si>
+  <si>
+    <t>4D4+SRV</t>
+  </si>
+  <si>
+    <t>9 TILES</t>
+  </si>
+  <si>
+    <t>STONE HAMMER</t>
+  </si>
+  <si>
+    <t>Replace your/your ally's next ATK roll with a 2D6+(caster's) SRV Crush DMG roll. This ATK may Stagger targets (resist with VIT 18+).</t>
+  </si>
+  <si>
+    <t>Encase a weapon or piece of ammunition in dense stone adding great impact to its next strike</t>
+  </si>
+  <si>
+    <t>SPORE SPLASH</t>
+  </si>
+  <si>
+    <t>Target must also make a VIT save (15+) or suffer the Sleep status effect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conjure colorful, fungal spores in your hands and fling them at an enemy </t>
+  </si>
+  <si>
+    <t>2D6+SRV</t>
+  </si>
+  <si>
     <t>2 TILES</t>
   </si>
   <si>
-    <t>BURN IMPURITIES</t>
-  </si>
-  <si>
-    <t>Deal 1D4 Fire DMG to yourself and cure yourself of Poison and Freeze buildup.</t>
-  </si>
-  <si>
-    <t>Summon an inner flame that burns away the toxins of the body and cures frostbite</t>
-  </si>
-  <si>
-    <t>HEAL</t>
-  </si>
-  <si>
-    <t>CONSUME FLAMES</t>
-  </si>
-  <si>
-    <t>If your target is suffering from the burned status effect cure it and heal them and yourself for 1D4 HP.</t>
-  </si>
-  <si>
-    <t>Seize control of a flame being used against you and empower yourself with its essence</t>
-  </si>
-  <si>
-    <t>SELF/ALLY (MELEE)</t>
-  </si>
-  <si>
-    <t>FORGE-FIRE</t>
-  </si>
-  <si>
-    <t>Deals an additional pt. of direct DMG per 1 pt. of equipped ARM your target has.</t>
-  </si>
-  <si>
-    <t>Engulf your target in a molten flame that heats metal and flesh like a blacksmith's forge</t>
-  </si>
-  <si>
-    <t>3 TILES</t>
-  </si>
-  <si>
-    <t>SURGING FLAME</t>
-  </si>
-  <si>
-    <t>Increase the Cast Requirement by up to 4 pts. Adding 2 fire DMG to this spell per pt. increase. The additions must be called before the cast is rolled.</t>
-  </si>
-  <si>
-    <t>Cradle this flame and charge it with your own magic power allowing it to grow in strength as well as instability</t>
-  </si>
-  <si>
-    <t>1D8 (+)</t>
-  </si>
-  <si>
-    <t>3 TILES (WIDTH)</t>
-  </si>
-  <si>
-    <t>[ ADVANCED LEVEL : 2 SPELL MEMORY TO LEARN ]</t>
-  </si>
-  <si>
-    <t>GREATER STAR FIRE</t>
-  </si>
-  <si>
-    <t>Deals 1D8 fire DMG to units within 1 tile of target area as well; Can deal 1D8 fire DMG to yourself to lower the Cast Cost to 6 (can be called during the spellcast).</t>
-  </si>
-  <si>
-    <t>Conjure a destructive missile of flame at your fingertips and fling it towards an enemy</t>
-  </si>
-  <si>
-    <t>2D8+SRV</t>
-  </si>
-  <si>
-    <t>NOXIOUS FLAME</t>
-  </si>
-  <si>
-    <t>Target must succeed a SPD save (16+) or suffer an additional 1D8 Toxic DMG</t>
-  </si>
-  <si>
-    <t>Conjure a foul flame that burns bright green with unnatural toxins</t>
-  </si>
-  <si>
-    <t>1D10+SRV</t>
-  </si>
-  <si>
-    <t>FIRE (TOXIC)</t>
-  </si>
-  <si>
-    <t>3+ACC</t>
-  </si>
-  <si>
-    <t>INFERNO</t>
-  </si>
-  <si>
-    <t>Cause the Inferno weather effect to appear within the area of the battlefield for 1D4+SRV rounds (see combat doc. for weather effects).</t>
-  </si>
-  <si>
-    <t>Blanket the area in an atmosphere so hot it ignites foliage and evaporates nearby water</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>COMET DASH</t>
-  </si>
-  <si>
-    <t>Teleport to a new tile 5 tiles away in a line. Deals DMG to all targets within linear range; targets can avoid DMG with a SPD save (18+).</t>
-  </si>
-  <si>
-    <t>Surround yourself with flames and jettison yourself forward scorching everything in your blazing path</t>
-  </si>
-  <si>
-    <t>4 TILES (LINEAR)</t>
-  </si>
-  <si>
-    <t>MAGMA MISSILE</t>
-  </si>
-  <si>
-    <t>Lower target's Fire resistance to 0 after this spell's DMG is dealt (unless they are fully immune). Lasts 1+SRV rounds.</t>
-  </si>
-  <si>
-    <t>Blast an opponent with a sizzling bolt of molten gel that leaves their defenses melted</t>
-  </si>
-  <si>
-    <t>WHITE FLAME</t>
-  </si>
-  <si>
-    <t>Revive a dead party member to 1 HP. Can deal 1D10 Fire DMG to self to lower the cast cost to 6.</t>
-  </si>
-  <si>
-    <t>Summon a wisp of the White Flame of Iridess to guide a wayward spirit back to its body</t>
-  </si>
-  <si>
-    <t>FLAME OF THE DEATHBLIGHT</t>
-  </si>
-  <si>
-    <t>Deals an additional 2D6 Mind DMG unless the target makes a successful MEM save (12+).</t>
-  </si>
-  <si>
-    <t>Call upon the soul-scorching fires controlled by the God of the Corrupted Dead, Mhire</t>
-  </si>
-  <si>
-    <t>FIRE (MIND)</t>
-  </si>
-  <si>
-    <t>2+VIT TILES</t>
-  </si>
-  <si>
-    <t>DAWN'S BLAZE</t>
-  </si>
-  <si>
-    <t>Deals an additional HD10 Fire DMG if the target is at their maximum HP.</t>
-  </si>
-  <si>
-    <t>Cast a bright flame that burns stronger as a first-strike like the first rays of the sun at dawn</t>
-  </si>
-  <si>
-    <t>BURNING EARTH</t>
-  </si>
-  <si>
-    <t>Create up to 3 Fire Tiles within the designated range. If a unit is standing on one of these tiles they can make a SPD save (13+) to jump to an adjacent tile.</t>
-  </si>
-  <si>
-    <t>Ignite the very ground you walk upon to trap your foes in a great burning blaze</t>
-  </si>
-  <si>
-    <t>1 TILE (X3)</t>
-  </si>
-  <si>
-    <t>MELTDOWN</t>
-  </si>
-  <si>
-    <t>Deals an additional HD10 direct DMG to targets with a Fire weakness at the expense of dealing 1D6 Direct DMG to yourself.</t>
-  </si>
-  <si>
-    <t>Sacrifice your own vitality as fuel to conjure a devastating blaze that burns beyond physical abjuration.</t>
-  </si>
-  <si>
-    <t>[ MASTER LEVEL : 3 SPELL MEMORY TO LEARN ]</t>
-  </si>
-  <si>
-    <t>GRAND STAR FIRE</t>
-  </si>
-  <si>
-    <t>Deals 1D10 fire DMG to units within 1 tile of target area as well; Can deal 1D10 fire DMG to yourself to lower the Cast Cost to 6 (can be called during the spellcast).</t>
-  </si>
-  <si>
-    <t>Fire a screeching bolt of white-hot flame out of the hands that impacts your victim like a burning meteorite</t>
-  </si>
-  <si>
-    <t>3D8+SRV</t>
-  </si>
-  <si>
-    <t>PYROCLASTIC LIGHTNING</t>
-  </si>
-  <si>
-    <t>Targets within a 3x3 area of the main target make a SPD save (20+) or suffer 2D10 Electric DMG</t>
-  </si>
-  <si>
-    <t>Create an explosion of flame so powerful that it causes red arcs of volcanic lightning to appear</t>
-  </si>
-  <si>
-    <t>2D10+SRV</t>
-  </si>
-  <si>
-    <t>FIRE (ELECTRIC)</t>
-  </si>
-  <si>
-    <t>1 TARGET (3X3 AREA)</t>
-  </si>
-  <si>
-    <t>NOVA</t>
-  </si>
-  <si>
-    <t>Deals DMG to all in range / area. Destroys any destructible objects, tiles or obstacles in area.</t>
-  </si>
-  <si>
-    <t>Decimate a large area of the battlefield with a scorching explosion</t>
-  </si>
-  <si>
-    <t>10 TILES</t>
-  </si>
-  <si>
-    <t>5X5 AREA</t>
-  </si>
-  <si>
-    <t>FUNERAL PYRE</t>
-  </si>
-  <si>
-    <t>Can only be cast right when you are brought to 0 HP; This spell can not be charged. Deal DMG to all enemy units within a 5x5 area and add 1D6 to your Fate Roll.</t>
-  </si>
-  <si>
-    <t>(3D6+SRV)</t>
-  </si>
-  <si>
-    <t>METEORITE</t>
-  </si>
-  <si>
-    <t>Additionally takes 1 Stamina to cast; This spell can harm allied units regardless of defensive skills or other measures. Destroys all breakable objects/tiles in area.</t>
-  </si>
-  <si>
-    <t>5D10+SRV</t>
-  </si>
-  <si>
-    <t>30 TILES</t>
-  </si>
-  <si>
-    <t>SUNLIGHT BEAM</t>
-  </si>
-  <si>
-    <t>Deals DMG to all in the area; Deals an additional 1D8 Light DMG unless target(s) make a STR save (18+).</t>
-  </si>
-  <si>
-    <t>FIRE (LIGHT)</t>
-  </si>
-  <si>
-    <t>10 TILES (LINEAR)</t>
-  </si>
-  <si>
-    <t>FIRES OF CREATION</t>
-  </si>
-  <si>
-    <t>Perform an Armorer action using gear / materials you have on hand without having to rest or camp.</t>
-  </si>
-  <si>
-    <t>OCEAN'S CALL ARCANA</t>
-  </si>
-  <si>
-    <t>GEYSER</t>
-  </si>
-  <si>
-    <t>Units within the 3x3 Area around the initial geyser must make a SPD save (15+) or they take 1D6 water DMG. Create water tiles on unoccupied tiles within 3x3 area.</t>
-  </si>
-  <si>
-    <t>Cause an eruption of water to breach the ground splashing an area with destructive force</t>
-  </si>
-  <si>
-    <t>1D8+VIT</t>
-  </si>
-  <si>
-    <t>WATER</t>
-  </si>
-  <si>
-    <t>FROST MISSILE</t>
-  </si>
-  <si>
-    <t>Reduce target's MOVE by 1 for 2 rounds (effect can stack up to 3 times).</t>
-  </si>
-  <si>
-    <t>Launch an icy projectile from your hands that bursts into a biting blast of frost when it finds its mark</t>
-  </si>
-  <si>
-    <t>ICE</t>
-  </si>
-  <si>
-    <t>ARMOR OF WINTER</t>
-  </si>
-  <si>
-    <t>Grants +2 ARM. ARM is reduced by 1 each time the buffed unit is hit. Fire / Crush DMG removes this buff completely.</t>
-  </si>
-  <si>
-    <t>Solidify plates of ice around the body granting a temporary but sturdy bit of defense</t>
-  </si>
-  <si>
-    <t>WATER VEIL</t>
-  </si>
-  <si>
-    <t>Grants +1 BAR and Water / Ice resistance (1) for the next 1+VIT rounds.</t>
-  </si>
-  <si>
-    <t>Create a cloak of glowing water that filters magical energy and absorbs cold</t>
-  </si>
-  <si>
-    <t>ICE BLADE</t>
-  </si>
-  <si>
-    <t>Blade is treated like an equipped weapon (replaces channeling item). Has the stats of the spell effect. Lasts 1D4+VIT rounds. Can be used in the same action when summoned.</t>
-  </si>
-  <si>
-    <t>Form a deadly-sharp blade of ice over your staff or wand and wield it like a crude scimitar</t>
-  </si>
-  <si>
-    <t>1D6+VIT</t>
-  </si>
-  <si>
-    <t>SLASH +ICE</t>
-  </si>
-  <si>
-    <t>GLACIATE</t>
-  </si>
-  <si>
-    <t>Create Ice Tiles within the chosen 2x2 Area.</t>
-  </si>
-  <si>
-    <t>Freeze a small patch of ground nearby to obstruct foes or quell flames</t>
-  </si>
-  <si>
-    <t>5 TILES</t>
-  </si>
-  <si>
-    <t>2X2 AREA</t>
-  </si>
-  <si>
-    <t>ICE PILLAR</t>
-  </si>
-  <si>
-    <t>Create a pillar of ice equal to 1 lv. of elevation; Can be created on a unit's tile. Pillar has 12 HP, Fire / Crush weak (2), Water/Ice/Pierce resist (2).</t>
-  </si>
-  <si>
-    <t>Raise a column of hard-packed ice to reach greater heights or better defend and area</t>
-  </si>
-  <si>
-    <t>5+VIT TILES</t>
-  </si>
-  <si>
-    <t>1 TILE</t>
-  </si>
-  <si>
-    <t>PRESSURE BUBBLE</t>
-  </si>
-  <si>
-    <t>Target takes an additional 1D6 Crush DMG unless they succeed a VIT save (12+). Create a water tile on targeted space.</t>
-  </si>
-  <si>
-    <t>Form a bubble filled with the pressure of the ocean depths and burst it, unleashing a rippling pulse</t>
-  </si>
-  <si>
-    <t>WATER (CRUSH)</t>
-  </si>
-  <si>
-    <t>WATER WHIP</t>
-  </si>
-  <si>
-    <t>Create a water tile on the targeted space. Target must make a SPD save (10+) or their STR is lowered by 1 for 2 rounds.</t>
-  </si>
-  <si>
-    <t>Draw water from the air around you and form it into a painful whip</t>
-  </si>
-  <si>
-    <t>2 TILE MELEE</t>
-  </si>
-  <si>
-    <t>CASCADE</t>
-  </si>
-  <si>
-    <t>Deals DMG to all units in range; Units that take DMG must also make a SPD save (14+) or get knocked back in the direction of the attack 2 tiles.</t>
-  </si>
-  <si>
-    <t>Summon a forceful stream of water that crashes into foes like a rushing river</t>
-  </si>
-  <si>
-    <t>5 TILES (LINEAR)</t>
-  </si>
-  <si>
-    <t>1 TILE (LINEAR)</t>
-  </si>
-  <si>
-    <t>CLEAR SKIES</t>
-  </si>
-  <si>
-    <t>End any active weather effect within the battlefield area. If this weather is a persistent part of the area/dungeon it returns in 1D4+VIT rounds.</t>
-  </si>
-  <si>
-    <t>Send a magic wave skyward that dispels turbulent weather clearing the skies above you</t>
-  </si>
-  <si>
-    <t>DOUSE</t>
-  </si>
-  <si>
-    <t>Cure the target of the burned status. Grant your target Fire resist (1) and electric weakness (1). Lasts 2 rounds.</t>
-  </si>
-  <si>
-    <t>Conjure a small rain cloud above your target bathing them in water</t>
-  </si>
-  <si>
-    <t>HEAL / DEBUFF</t>
-  </si>
-  <si>
-    <t>HYDRATION</t>
-  </si>
-  <si>
-    <t>Restore 1D6 HP to all allied units within 2 spaces of a water tile or to all allies if the Rain weather effect is active.</t>
-  </si>
-  <si>
-    <t>Absorb the healing waters touching the skin like a thirsting flower</t>
-  </si>
-  <si>
-    <t>SELF/ALLY</t>
-  </si>
-  <si>
-    <t>(ALL)</t>
-  </si>
-  <si>
-    <t>RAINFALL</t>
-  </si>
-  <si>
-    <t>Cause the Rain weather effect to appear within the area of the battlefield for 1D4+VIT rounds (see combat doc. for weather effects).</t>
-  </si>
-  <si>
-    <t>Create your own miniature rain storm, forming gray clouds above your area</t>
-  </si>
-  <si>
-    <t>FROST TOMB</t>
-  </si>
-  <si>
-    <t>Target suffers 1D4 pts. of the Freeze status buildup.</t>
-  </si>
-  <si>
-    <t>Freeze the air around an enemy encasing them in a tomb of ice</t>
-  </si>
-  <si>
-    <t>2D6+VIT</t>
-  </si>
-  <si>
-    <t>3+VIT TILES</t>
-  </si>
-  <si>
-    <t>GLACIAL LANCE</t>
-  </si>
-  <si>
-    <t>Pierce DMG ignores target's Pierce resistance by 1 level ; Deals an additional 1D6 Ice DMG if this spell was cast in 1 turn.</t>
-  </si>
-  <si>
-    <t>Form a spear of lethally sharp ice and launch it at your opponent, rending them and chilling them simultaneously</t>
-  </si>
-  <si>
-    <t>1D10+VIT</t>
-  </si>
-  <si>
-    <t>PIERCE (ICE)</t>
-  </si>
-  <si>
-    <t>TIDAL SWEEP</t>
-  </si>
-  <si>
-    <t>Damages all within the area (spell is always centered on the caster).</t>
-  </si>
-  <si>
-    <t>Summon a great wave that crushes all within its bredth</t>
-  </si>
-  <si>
-    <t>2D8+VIT</t>
-  </si>
-  <si>
-    <t>5 TILES (WIDTH)</t>
-  </si>
-  <si>
-    <t>SHARD STORM</t>
-  </si>
-  <si>
-    <t>Target(s) must make a VIT save (17+) or suffer the Needled status effect.</t>
-  </si>
-  <si>
-    <t>Crystalize and freeze the air above your enemies causing needles of solid ice to fall upon them</t>
-  </si>
-  <si>
-    <t>3D4+VIT</t>
-  </si>
-  <si>
-    <t>4+VIT TILES</t>
-  </si>
-  <si>
-    <t>FLOOD</t>
-  </si>
-  <si>
-    <t>Deals DMG to all enemy units- Does not harm allied units; Destroys all fire tiles in the area.</t>
-  </si>
-  <si>
-    <t>Conjure the power of violent floodwaters sweeping away your enemies while gently passing over your allies</t>
-  </si>
-  <si>
-    <t>WATER FORM</t>
-  </si>
-  <si>
-    <t>Melt into a puddle of water; You can move to any connected water tiles freely. You are immune to all DMG but Electric in this form (lasts 2 rounds or until ended by caster).</t>
-  </si>
-  <si>
-    <t>Transmute your body into liquid water allowing you to meld with other sources and avoid detection</t>
-  </si>
-  <si>
-    <t>GREAT GEYSER</t>
-  </si>
-  <si>
-    <t>Units within the 3x3 Area around the initial geyser must make a SPD save (16+) or they take 1D8 water DMG.</t>
-  </si>
-  <si>
-    <t>Cause a massive eruption of water to breach the ground splashing an area with destructive force</t>
-  </si>
-  <si>
-    <t>FREEZE</t>
-  </si>
-  <si>
-    <t>Target suffers 2D4 pts. of the Freeze status buildup.</t>
-  </si>
-  <si>
-    <t>Grasp your target, freezing them with a magic chill</t>
-  </si>
-  <si>
-    <t>STATUS EFFECT</t>
-  </si>
-  <si>
-    <t>COMPACTION</t>
-  </si>
-  <si>
-    <t>Deals DMG to all enemy units suffering from any Freeze buildup; Fully frozen targets take an additional 1D6 DMG. This ends the target's freeze buildup/effect.</t>
-  </si>
-  <si>
-    <t>Reach out and take control of the frost covering your freezing prey and clamp the elemental ice down upon them</t>
-  </si>
-  <si>
-    <t>(3D6+VIT)</t>
-  </si>
-  <si>
-    <t>CRUSH</t>
-  </si>
-  <si>
-    <t>(?)</t>
-  </si>
-  <si>
-    <t>SPELL NAME</t>
-  </si>
-  <si>
-    <t>GREAT STORM ARTS</t>
-  </si>
-  <si>
-    <t>SHOCKING DART</t>
-  </si>
-  <si>
-    <t>Fire a small bolt of electricity that travels through the air and finds its mark near-instantly</t>
-  </si>
-  <si>
-    <t>1D4+SPD</t>
-  </si>
-  <si>
-    <t>ELECTRIC</t>
-  </si>
-  <si>
-    <t>12 TILES</t>
-  </si>
-  <si>
-    <t>AIR BLAST</t>
-  </si>
-  <si>
-    <t>Targets within area who do not fully resist this spells' DMG are knocked back 1D4 tiles.</t>
-  </si>
-  <si>
-    <t>Call forth a powerful wind that sends everything in front of you reeling backward</t>
-  </si>
-  <si>
-    <t>1D6+SPD</t>
-  </si>
-  <si>
-    <t>WIND</t>
-  </si>
-  <si>
-    <t>VENTILATION</t>
-  </si>
-  <si>
-    <t>Clear the battlefield of smoke, fog, poison mist, or any other gaseous substance that linger on the battlefield.</t>
-  </si>
-  <si>
-    <t>Summon a sweeping gust of wind that encircles the area cleansing it of smoke and dust</t>
-  </si>
-  <si>
-    <t>FRESH AIR</t>
-  </si>
-  <si>
-    <t>Restore 1D4 HP and cleanse the target of any coated substances (water, oil, etc.)</t>
-  </si>
-  <si>
-    <t>Call a soothing magic wind to restore vitality and loose foreign substances from the body</t>
-  </si>
-  <si>
-    <t>SELF/ALLY (5 TILES)</t>
-  </si>
-  <si>
-    <t>THUNDER ECHO</t>
-  </si>
-  <si>
-    <t>Targets within area also take 1D6 Sound DMG unless they succeed a VIT save (13+).</t>
-  </si>
-  <si>
-    <t>Call down a miniature bolt of lightning followed by a booming echo of thunder</t>
-  </si>
-  <si>
-    <t>ELECTRIC (SOUND)</t>
-  </si>
-  <si>
-    <t>ZEPHYR</t>
-  </si>
-  <si>
-    <t>Destroys fire tiles within a 3x3 area of your target.</t>
-  </si>
-  <si>
-    <t>Surround an enemy in a violent spiral of cutting wind</t>
-  </si>
-  <si>
-    <t>ELECTROCUTE</t>
-  </si>
-  <si>
-    <t>Target must also make a VIT save (11+) or drop their equipped weapon(s).</t>
-  </si>
-  <si>
-    <t>Grasp your quarry with hands charged with crackling blue electricity</t>
-  </si>
-  <si>
-    <t>1D8+SPD</t>
-  </si>
-  <si>
-    <t>CLOUD LEAP</t>
-  </si>
-  <si>
-    <t>Gain fall DMG immunity. Target's jump distance is buffed to 4+STR tiles and 2 levels of elevation. Lasts 1D4+SPD rounds.</t>
-  </si>
-  <si>
-    <t>Summon an enchanted wind to carry your jumps further and protect you from plummeting</t>
-  </si>
-  <si>
-    <t>SELF/ALLY (7 TILES)</t>
-  </si>
-  <si>
-    <t>BLUSTER CLOAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranged weapon ATKs (that deal pierce, slash or crush DMG) have disadvantage against the buffed target. Lasts 1D4 rounds.  </t>
-  </si>
-  <si>
-    <t>Wreathe yourself in swirling winds that deflect incoming projectiles</t>
-  </si>
-  <si>
-    <t>ENERGIZE</t>
-  </si>
-  <si>
-    <t>Increase target's MOVE and EVA by 1 for 1+ (target's) SPD rounds.</t>
-  </si>
-  <si>
-    <t>Charge your muscles with magical electric impulses that aid in reaction and speed</t>
-  </si>
-  <si>
-    <t>ARCING SHIELD</t>
-  </si>
-  <si>
-    <t>When melee DMG / a Martial Maneuver is dealt to the buffed unit deal 1D6 elec. DMG back to the attacker (attacker can evade with SPD 15+). Lasts 3 rounds.</t>
-  </si>
-  <si>
-    <t>Temporarily enchant an equipped garb with a magic charge able to retaliate with shocks toward an attacker</t>
-  </si>
-  <si>
-    <t>(ELEC)</t>
-  </si>
-  <si>
-    <t>THUNDER FIST</t>
-  </si>
-  <si>
-    <t>Target must make a VIT save (13+) or become staggered for 1 round.</t>
-  </si>
-  <si>
-    <t>Release a booming ripple of thunder from a closed, concentrated fist</t>
-  </si>
-  <si>
-    <t>SOUND</t>
-  </si>
-  <si>
-    <t>SPLITTING BOLT</t>
-  </si>
-  <si>
-    <t>Spell can hit up to 3 targets; Only 1 target per projectile.</t>
-  </si>
-  <si>
-    <t>Fire sparks of electricity that split into three arcs that chase their targets with ferocity</t>
-  </si>
-  <si>
-    <t>ELEC</t>
-  </si>
-  <si>
-    <t>3+SPD TILES</t>
-  </si>
-  <si>
-    <t>LIGHTNING BOLT</t>
-  </si>
-  <si>
-    <t>DMG ignores BAR and can not miss unless the target is fully immune to spell DMG / electric DMG in some way.</t>
-  </si>
-  <si>
-    <t>Call down a devastating bolt of lightning on your enemy striking them with the elemental ferocity of nature herself</t>
-  </si>
-  <si>
-    <t>2D10+SPD</t>
-  </si>
-  <si>
-    <t>ELECTRIFICATION CIRCLE</t>
-  </si>
-  <si>
-    <t>Allied units standing within circle add 1D6 electric DMG to any ATKs / spells used. Lasts 2+(caster's)SPD rounds.</t>
-  </si>
-  <si>
-    <t>Summon a magic circle of lightning that infuses spells, arrows and blades with the power of the storm</t>
-  </si>
-  <si>
-    <t>(ELECTRIC)</t>
-  </si>
-  <si>
-    <t>DOWNDRAFT</t>
-  </si>
-  <si>
-    <t>Launch yourself into the air avoiding enemies and tiles on the ground; Land safely on a space up to 5 tiles away (elevation adds +1 move distance)</t>
-  </si>
-  <si>
-    <t>Expel a blast of air downward launching yourself into the sky and away from danger</t>
-  </si>
-  <si>
-    <t>2D6+SPD</t>
-  </si>
-  <si>
-    <t>BOLT JUMP</t>
-  </si>
-  <si>
-    <t>Teleport to a space within 10 tiles. Deal 1D6+SPD Electric DMG to any targets within 1 tile of your chosen warp point.</t>
-  </si>
-  <si>
-    <t>Convert your body into pure electricity and jump to a distant space</t>
-  </si>
-  <si>
-    <t>(1D6+SPD)</t>
-  </si>
-  <si>
-    <t>(1 TILE RADIUS)</t>
-  </si>
-  <si>
-    <t>ARCING BOLT</t>
-  </si>
-  <si>
-    <t>Deals DMG to all in range / area.</t>
-  </si>
-  <si>
-    <t>Cast out a flurry of dancing electric bolts that fan out in a wide area of destruction</t>
-  </si>
-  <si>
-    <t>2D8+SPD</t>
-  </si>
-  <si>
-    <t>3 TILES (LINEAR)</t>
-  </si>
-  <si>
-    <t>LIGHTNING STORM</t>
-  </si>
-  <si>
-    <t>Cause the Lightning Storm weather effect to appear within the area of the battlefield for 1D4+SPD rounds (see combat doc. for weather effects).</t>
-  </si>
-  <si>
-    <t>Summon a localized storm of elemental lightning, dangerous and untamable</t>
-  </si>
-  <si>
-    <t>LIGHTNING ROD</t>
-  </si>
-  <si>
-    <t>Target is struck by the next lightning bolt that occurs during the Lightning Storm weather effect (effect ends after target is struck).</t>
-  </si>
-  <si>
-    <t>Mark your target with an invisible thread connecting them to the electricity in the sky above</t>
-  </si>
-  <si>
-    <t>CONDUCTIVE AURA</t>
-  </si>
-  <si>
-    <t>Draw any electric DMG being dealt by enemy units towards yourself and gain Electric resistance (2). Lasts 2+INT rounds.</t>
-  </si>
-  <si>
-    <t>Cast a force around you that conducts all electricity on the battlefield</t>
-  </si>
-  <si>
-    <t>DERECHO</t>
-  </si>
-  <si>
-    <t>Summon a vortex of crushing winds that decimates all enemies and spares friendly combatants</t>
-  </si>
-  <si>
-    <t>1D10+SPD</t>
-  </si>
-  <si>
-    <t>GALE CIRCLE</t>
-  </si>
-  <si>
-    <t>Can be cast on an unoccupied tile as a trap (sprung when tile walked over). Target must also make a SPD save (17+) or become Staggered.</t>
-  </si>
-  <si>
-    <t>Create a swirl of wind on the ground that contains the power of a small tornado waiting to spring forth</t>
-  </si>
-  <si>
-    <t>7 TILES (SPAWN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>LIGHTNING BEAM</t>
-  </si>
-  <si>
-    <t>Beam damages all within the 6 tile line. Can be cast through objects / other units.</t>
-  </si>
-  <si>
-    <t>Fire a deadly ray of electricity from your palms that shoots right through everything in its way</t>
-  </si>
-  <si>
-    <t>6 TILES (LINEAR)</t>
-  </si>
-  <si>
-    <t>CYCLONE</t>
-  </si>
-  <si>
-    <t>7D6+SPD</t>
-  </si>
-  <si>
-    <t>6X6 AREA</t>
-  </si>
-  <si>
-    <t>ARCANE CHARGE</t>
-  </si>
-  <si>
-    <t>Return 1D4 pts. of charge to a magic item within range.</t>
-  </si>
-  <si>
-    <t>CHAIN LIGHTNING</t>
-  </si>
-  <si>
-    <t>1 DMG roll is made; Deals DMG to any other enemy units within 3 tiles of the original target unit.</t>
-  </si>
-  <si>
-    <t>2D12+SPD</t>
-  </si>
-  <si>
-    <t>1 (+) TARGET(S)</t>
-  </si>
-  <si>
-    <t>ACCELERATION</t>
-  </si>
-  <si>
-    <t>Grants target an additional slot in the turn order; A new Initiative roll is made for this slot (extra turn is removed from turn order after 2 rounds).</t>
-  </si>
-  <si>
-    <t>HEART SHOCK</t>
-  </si>
-  <si>
-    <t>Revive a KO'd or dead ally to 1 HP.</t>
-  </si>
-  <si>
-    <t>ALLY (MELEE)</t>
-  </si>
-  <si>
-    <t>CRASH BOLT</t>
-  </si>
-  <si>
-    <t>Target also becomes staggered unless they succeed a VIT save (20+).</t>
-  </si>
-  <si>
-    <t>Catch a falling bolt of lightning and form it into a condensed ball of explosive electric energy</t>
-  </si>
-  <si>
-    <t>8 TILES</t>
-  </si>
-  <si>
-    <t>ARCADIAN ARTS</t>
-  </si>
-  <si>
-    <t>SPLINTER STONE</t>
-  </si>
-  <si>
-    <t>Target(s) must make a SPD save (11+) or suffer the Needled status effect.</t>
-  </si>
-  <si>
-    <t>Acquire a nearby rock, brick or other mineral material and cause it to explode into sharp shards</t>
-  </si>
-  <si>
-    <t>PIERCE</t>
-  </si>
-  <si>
-    <t>TANGLE VINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increase Cast Cost by 2 to add another target that is within range (up to 3 targets). Immobilize target(s) until they make a STR check of 10+ on their turn. </t>
-  </si>
-  <si>
-    <t>Call spiraling vines to sprout from below that grasp at anything they touch</t>
-  </si>
-  <si>
-    <t>5+SRV TILES</t>
-  </si>
-  <si>
-    <t>1-? TARGETS</t>
-  </si>
-  <si>
-    <t>OIL STREAM</t>
-  </si>
-  <si>
-    <t>Covers the target in oil granting fire weakness (1) for 2 rounds unless the target succeeds a SPD save (12+).</t>
-  </si>
-  <si>
-    <t>Cause a small eruption of oil to burst from below an enemy coating them in flammable black tar.</t>
-  </si>
-  <si>
-    <t>SWARM</t>
-  </si>
-  <si>
-    <t>At the end of the caster's turn deals 1D4+SRV Toxic DMG or moves to closest enemy unit after initial target dies. Lasts 1D4 rounds.</t>
-  </si>
-  <si>
-    <t>Call a cloud of biting insects to your aid that tenaciously swarms your enemies</t>
-  </si>
-  <si>
-    <t>SUMMON</t>
-  </si>
-  <si>
-    <t>TOXIC</t>
-  </si>
-  <si>
-    <t>3 TILES (SPAWN)</t>
-  </si>
-  <si>
-    <t>1 TARGET (AT A TIME)</t>
-  </si>
-  <si>
-    <t>ROCK LAUNCH</t>
-  </si>
-  <si>
-    <t>Target must also make a VIT save (14+) or suffer the Staggered status effect.</t>
-  </si>
-  <si>
-    <t>Tear a chunk of earth out of the ground and launch it at a foe with magic-enhanced strength</t>
-  </si>
-  <si>
-    <t>2+STR TILES</t>
-  </si>
-  <si>
-    <t>STINGER TRAP</t>
-  </si>
-  <si>
-    <t>Can be cast on an unoccupied tile as a trap (sprung when tile walked over). Target must also make a SPD save (12+) or their turn immediately ends and they become Poisoned.</t>
-  </si>
-  <si>
-    <t>Compel a swarm of scorpions to ambush your enemies, piercing them with venom-filled stingers</t>
-  </si>
-  <si>
-    <t>1D4+SRV</t>
-  </si>
-  <si>
-    <t>8 TILES (SPAWN)</t>
-  </si>
-  <si>
-    <t>LEAF CUTTER</t>
-  </si>
-  <si>
-    <t>This spell ignores 1 level of the target's Slash resistance</t>
-  </si>
-  <si>
-    <t>Momentarily transform a simple leaf or flower petal into a razor-sharp blade</t>
-  </si>
-  <si>
-    <t>SLASH</t>
-  </si>
-  <si>
-    <t>ACID DART</t>
-  </si>
-  <si>
-    <t>Deals an additional 1D6 toxic DMG to targets with a BAR value of 0.</t>
-  </si>
-  <si>
-    <t>Form an arrow of bubbling green acid in your hand and fire it towards an enemy</t>
-  </si>
-  <si>
-    <t>FORAGER'S FRIEND</t>
-  </si>
-  <si>
-    <t>Can only be cast at camp (uses camp action); Create edible plants that restore 1D4 Stamina to the party.</t>
-  </si>
-  <si>
-    <t>Grow a bushel of hardy, nutritious vegetables to help keep your party fed</t>
-  </si>
-  <si>
-    <t>THORN WOOD</t>
-  </si>
-  <si>
-    <t>Cast on a target's weapon has wood as it's material type grant it +1D4 toxic DMG and a buff that poisons those struck with it (target can save from poison effect with VIT 12+). Lasts 1D4+SRV rounds.</t>
-  </si>
-  <si>
-    <t>Coax venomous thorns to sprout from the wood of your weapons, granting them poisonous properties</t>
-  </si>
-  <si>
-    <t>(TOXIC)</t>
-  </si>
-  <si>
-    <t>BRITTLE BEAM</t>
-  </si>
-  <si>
-    <t>Lowers target's Crush and Pierce resistance by 1 level for 2 rounds if they took DMG from this spell (does not cause Crush/Pierce weakness).</t>
-  </si>
-  <si>
-    <t>Fire an acidic-green ray that melts small holes in hide and armor</t>
-  </si>
-  <si>
-    <t>CALM ELEMENTS</t>
-  </si>
-  <si>
-    <t>Cure a target of the burned and frozen statuses.</t>
-  </si>
-  <si>
-    <t>Dispel harmful elemental effects from the body, returning their energies to nature</t>
-  </si>
-  <si>
-    <t>VULNERARY</t>
-  </si>
-  <si>
-    <t>Allied units can consume a plant using an instant action to heal 1D4+(caster's) SRV HP. (1+SRV healing plants spawn upon casting).</t>
-  </si>
-  <si>
-    <t>Call forth a bushel of magical healing herbs from the ground that magically restore your party's vitality</t>
-  </si>
-  <si>
-    <t>EARTHEN ARMOR</t>
-  </si>
-  <si>
-    <t>Gain +3 temporary ARM; Lowers your EVA by 3 as well. Each time you are hit lower both of these effects by 1.</t>
-  </si>
-  <si>
-    <t>Form protective plates of stone across the body that protect the body from physical harm</t>
-  </si>
-  <si>
-    <t>CROW CALL</t>
-  </si>
-  <si>
-    <t>Targets take no DMG from this spell if they have any Lv. of Pierce resistance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Call upon a flock of night-black crows to assault a group of your enemies with sharp beaks and talons </t>
-  </si>
-  <si>
-    <t>4D4+SRV</t>
-  </si>
-  <si>
-    <t>9 TILES</t>
-  </si>
-  <si>
-    <t>STONE HAMMER</t>
-  </si>
-  <si>
-    <t>Replace your/your ally's next ATK roll with a 2D6+(caster's) SRV Crush DMG roll. This ATK may Stagger targets (resist with VIT 18+).</t>
-  </si>
-  <si>
-    <t>Encase a weapon or piece of ammunition in dense stone adding great impact to its next strike</t>
-  </si>
-  <si>
-    <t>SPORE SPLASH</t>
-  </si>
-  <si>
-    <t>Target must also make a VIT save (15+) or suffer the Sleep status effect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conjure colorful, fungal spores in your hands and fling them at an enemy </t>
-  </si>
-  <si>
-    <t>2D6+SRV</t>
-  </si>
-  <si>
     <t>WOLF CLAW</t>
   </si>
   <si>
@@ -1505,7 +1505,7 @@
     <t>Inflicts the staggered status if the target is an Undead enemy type.</t>
   </si>
   <si>
-    <t>An offesive spell crafted by Orthodoxy Tomb guardians; Disrupts the threads that connect the undead to our plane</t>
+    <t>An offensive spell crafted by Orthodoxy Tomb guardians; Disrupts the threads that connect the undead to our plane</t>
   </si>
   <si>
     <t>HANDS OF SHADOW</t>
@@ -1778,7 +1778,7 @@
     <t>Grant target advantage on all CHA checks made towards NPC's (except for "menace" checks). Lasts 1 conversation, transaction, or 1+CHA rounds if in combat.</t>
   </si>
   <si>
-    <t>Magically enchance ones charms, greasing the wheels of diplomacy.</t>
+    <t>Magically enhance one's charms, greasing the wheels of diplomacy.</t>
   </si>
   <si>
     <t>SPECTRAL KNIVES</t>
@@ -1982,7 +1982,7 @@
     <t>2 TILES (FORWARD)</t>
   </si>
   <si>
-    <t>DOPPLEGANGER</t>
+    <t>DOPPELGANGER</t>
   </si>
   <si>
     <t>Create a copy of yourself on an empty tile up to 5 tiles away. This copy has your exact stats, skills and equipment except its HP which is 1 and its initiative which is always 0.</t>
@@ -2048,7 +2048,7 @@
     <t>GIVE LIFE</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals 1D6 direct DMG to yourself and restore HP equal to triple the rolled value to an annlied unit within range. </t>
+    <t xml:space="preserve">Deals 1D6 direct DMG to yourself and restore HP equal to triple the rolled value to an allied unit within range. </t>
   </si>
   <si>
     <t>SELF/ALLY (10 TILES)</t>
@@ -3412,7 +3412,7 @@
         <v>20</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>38</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>31</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>5</v>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L53" s="10"/>
       <c r="M53" s="11"/>
       <c r="N53" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54">
@@ -3566,13 +3566,13 @@
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>20</v>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>5</v>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L58" s="10"/>
       <c r="M58" s="11"/>
       <c r="N58" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
@@ -3652,7 +3652,7 @@
         <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>26</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>5</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L63" s="10"/>
       <c r="M63" s="11"/>
       <c r="N63" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>13</v>
@@ -3738,7 +3738,7 @@
         <v>47</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="15"/>
@@ -3960,7 +3960,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4">
@@ -4015,13 +4015,13 @@
         <v>42</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="15"/>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -4098,10 +4098,10 @@
         <v>20</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>364</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="15"/>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14">
@@ -4175,7 +4175,7 @@
         <v>42</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>37</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19">
@@ -4252,16 +4252,16 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="F19" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>374</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
       <c r="N23" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24">
@@ -4332,13 +4332,13 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>26</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
       <c r="N28" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29">
@@ -4412,13 +4412,13 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>383</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>26</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34">
@@ -4495,7 +4495,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>47</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>5</v>
@@ -4557,12 +4557,12 @@
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L38" s="10"/>
       <c r="M38" s="11"/>
       <c r="N38" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39">
@@ -4575,10 +4575,10 @@
         <v>42</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>26</v>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>5</v>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="L43" s="10"/>
       <c r="M43" s="11"/>
       <c r="N43" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="44">
@@ -4697,7 +4697,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="38" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="49">
@@ -4735,10 +4735,10 @@
         <v>30</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>26</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>5</v>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="L53" s="10"/>
       <c r="M53" s="11"/>
       <c r="N53" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="54">
@@ -4815,10 +4815,10 @@
         <v>42</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>5</v>
@@ -4877,12 +4877,12 @@
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L58" s="10"/>
       <c r="M58" s="11"/>
       <c r="N58" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59">
@@ -4892,13 +4892,13 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>20</v>
@@ -4940,7 +4940,7 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>5</v>
@@ -4960,12 +4960,12 @@
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L63" s="10"/>
       <c r="M63" s="11"/>
       <c r="N63" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>20</v>
@@ -4984,7 +4984,7 @@
         <v>25</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="15"/>
@@ -5206,10 +5206,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -5223,7 +5223,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4">
@@ -5264,7 +5264,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>20</v>
@@ -5303,7 +5303,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -5323,12 +5323,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5338,13 +5338,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>413</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>414</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>38</v>
@@ -5383,7 +5383,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14">
@@ -5421,10 +5421,10 @@
         <v>30</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>20</v>
@@ -5463,7 +5463,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -5483,12 +5483,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19">
@@ -5498,13 +5498,13 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>421</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>26</v>
@@ -5581,7 +5581,7 @@
         <v>425</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>47</v>
@@ -5658,10 +5658,10 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>429</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>20</v>
@@ -5827,7 +5827,7 @@
         <v>14</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="15"/>
@@ -5898,10 +5898,10 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>43</v>
@@ -5978,16 +5978,16 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F49" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="15"/>
@@ -6284,10 +6284,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -6582,10 +6582,10 @@
         <v>20</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>20</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -6781,7 +6781,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -7249,13 +7249,13 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>26</v>
@@ -7329,13 +7329,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>458</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>26</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>462</v>
@@ -7489,13 +7489,13 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>26</v>
@@ -7569,13 +7569,13 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>458</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>26</v>
@@ -7649,13 +7649,13 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>26</v>
@@ -8049,13 +8049,13 @@
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>462</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>458</v>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>20</v>
@@ -8446,7 +8446,7 @@
         <v>451</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -8495,13 +8495,13 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>20</v>
@@ -8575,13 +8575,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>20</v>
@@ -8655,13 +8655,13 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>20</v>
@@ -8741,7 +8741,7 @@
         <v>458</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>26</v>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>20</v>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>20</v>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>462</v>
@@ -8984,7 +8984,7 @@
         <v>524</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="15"/>
@@ -9215,16 +9215,16 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>524</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="15"/>
@@ -9524,7 +9524,7 @@
         <v>451</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -9573,13 +9573,13 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>20</v>
@@ -9653,13 +9653,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>20</v>
@@ -9742,7 +9742,7 @@
         <v>544</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="15"/>
@@ -9819,10 +9819,10 @@
         <v>547</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -9899,10 +9899,10 @@
         <v>20</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="15"/>
@@ -10018,7 +10018,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -10492,10 +10492,10 @@
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="15"/>
@@ -10569,13 +10569,13 @@
         <v>558</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="15"/>
@@ -10649,7 +10649,7 @@
         <v>562</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>563</v>
@@ -10726,13 +10726,13 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>26</v>
@@ -10812,7 +10812,7 @@
         <v>20</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>26</v>
@@ -10889,10 +10889,10 @@
         <v>558</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>26</v>
@@ -10972,7 +10972,7 @@
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>38</v>
@@ -11049,7 +11049,7 @@
         <v>579</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>37</v>
@@ -11132,7 +11132,7 @@
         <v>20</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>26</v>
@@ -11292,7 +11292,7 @@
         <v>592</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>26</v>
@@ -11366,13 +11366,13 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>26</v>
@@ -11683,7 +11683,7 @@
         <v>551</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>20</v>
@@ -11978,7 +11978,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>20</v>
@@ -12135,7 +12135,7 @@
         <v>619</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>620</v>
@@ -12218,7 +12218,7 @@
         <v>624</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>26</v>
@@ -12458,7 +12458,7 @@
         <v>20</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>26</v>
@@ -12761,7 +12761,7 @@
         <v>551</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -12816,7 +12816,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>26</v>
@@ -12896,7 +12896,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>26</v>
@@ -12976,7 +12976,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>26</v>
@@ -13053,10 +13053,10 @@
         <v>643</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>38</v>
@@ -13139,7 +13139,7 @@
         <v>649</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="15"/>
@@ -13216,7 +13216,7 @@
         <v>20</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>20</v>
@@ -13255,7 +13255,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -13806,10 +13806,10 @@
         <v>658</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>38</v>
@@ -13963,10 +13963,10 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>649</v>
@@ -14049,10 +14049,10 @@
         <v>13</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="15"/>
@@ -14920,7 +14920,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -14934,7 +14934,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
@@ -15014,7 +15014,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -15034,12 +15034,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -15049,13 +15049,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>26</v>
@@ -15094,7 +15094,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -15135,10 +15135,10 @@
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="15"/>
@@ -15174,7 +15174,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -15209,16 +15209,16 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -15274,12 +15274,12 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
       <c r="N23" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
@@ -15289,13 +15289,13 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>26</v>
@@ -15334,7 +15334,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -15354,12 +15354,12 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
       <c r="N28" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>20</v>
@@ -15414,7 +15414,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -15434,12 +15434,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
@@ -15452,10 +15452,10 @@
         <v>12</v>
       </c>
       <c r="E34" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>102</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>103</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>26</v>
@@ -15494,7 +15494,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>5</v>
@@ -15514,12 +15514,12 @@
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L38" s="10"/>
       <c r="M38" s="11"/>
       <c r="N38" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39">
@@ -15574,7 +15574,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>5</v>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L43" s="10"/>
       <c r="M43" s="11"/>
       <c r="N43" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44">
@@ -15618,7 +15618,7 @@
         <v>14</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="15"/>
@@ -15654,7 +15654,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -15674,12 +15674,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49">
@@ -16047,13 +16047,13 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>26</v>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>547</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -17258,7 +17258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -17278,12 +17278,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
@@ -17338,7 +17338,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -17358,12 +17358,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -17373,16 +17373,16 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>123</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="15"/>
@@ -17418,7 +17418,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -17438,12 +17438,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -17453,16 +17453,16 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="15"/>
@@ -17498,7 +17498,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -17518,7 +17518,7 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>31</v>
@@ -17542,7 +17542,7 @@
         <v>43</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -17578,7 +17578,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
@@ -17613,16 +17613,16 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="15"/>
@@ -17658,7 +17658,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
@@ -17693,16 +17693,16 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E29" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="G29" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="15"/>
@@ -17738,7 +17738,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -17758,7 +17758,7 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
@@ -18480,7 +18480,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -18497,7 +18497,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -18517,12 +18517,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
@@ -18532,16 +18532,16 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="15"/>
@@ -18577,7 +18577,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -18597,12 +18597,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
@@ -18612,10 +18612,10 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>14</v>
@@ -18657,7 +18657,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -18677,12 +18677,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -18737,7 +18737,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -18757,12 +18757,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
@@ -18817,7 +18817,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -18837,12 +18837,12 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
       <c r="N23" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -18852,10 +18852,10 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>47</v>
@@ -18897,7 +18897,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -18917,12 +18917,12 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
       <c r="N28" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29">
@@ -18938,10 +18938,10 @@
         <v>20</v>
       </c>
       <c r="F29" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="15"/>
@@ -18977,7 +18977,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -18997,12 +18997,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34">
@@ -19018,10 +19018,10 @@
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="15"/>
@@ -19057,7 +19057,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>5</v>
@@ -19077,12 +19077,12 @@
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L38" s="10"/>
       <c r="M38" s="11"/>
       <c r="N38" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39">
@@ -19092,13 +19092,13 @@
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>26</v>
@@ -19137,7 +19137,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>5</v>
@@ -19157,12 +19157,12 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L43" s="10"/>
       <c r="M43" s="11"/>
       <c r="N43" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44">
@@ -19172,13 +19172,13 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>26</v>
@@ -19217,7 +19217,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -19237,12 +19237,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49">
@@ -19252,16 +19252,16 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="F49" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>185</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>186</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="15"/>
@@ -19297,7 +19297,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>5</v>
@@ -19317,12 +19317,12 @@
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L53" s="10"/>
       <c r="M53" s="11"/>
       <c r="N53" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54">
@@ -19338,10 +19338,10 @@
         <v>20</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="15"/>
@@ -19377,7 +19377,7 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>5</v>
@@ -19397,12 +19397,12 @@
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L58" s="10"/>
       <c r="M58" s="11"/>
       <c r="N58" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="59">
@@ -19412,13 +19412,13 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>26</v>
@@ -19460,7 +19460,7 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>5</v>
@@ -19480,12 +19480,12 @@
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L63" s="10"/>
       <c r="M63" s="11"/>
       <c r="N63" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64">
@@ -19495,16 +19495,16 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F64" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G64" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="H64" s="7"/>
       <c r="I64" s="15"/>
@@ -19726,10 +19726,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -19743,7 +19743,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -19763,12 +19763,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
@@ -19784,10 +19784,10 @@
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="15"/>
@@ -19823,7 +19823,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -19843,12 +19843,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
@@ -19858,13 +19858,13 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>206</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>26</v>
@@ -19903,7 +19903,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -19923,12 +19923,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
@@ -19938,10 +19938,10 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>210</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>211</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>14</v>
@@ -19983,7 +19983,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -20003,12 +20003,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19">
@@ -20018,16 +20018,16 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -20063,7 +20063,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -20083,12 +20083,12 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
       <c r="N23" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24">
@@ -20098,16 +20098,16 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>221</v>
-      </c>
       <c r="G24" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="15"/>
@@ -20143,7 +20143,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
       <c r="N28" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29">
@@ -20178,16 +20178,16 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="15"/>
@@ -20223,7 +20223,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -20243,12 +20243,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34">
@@ -20303,7 +20303,7 @@
     </row>
     <row r="38">
       <c r="A38" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>5</v>
@@ -20323,12 +20323,12 @@
       </c>
       <c r="H38" s="28"/>
       <c r="I38" s="30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L38" s="31"/>
       <c r="M38" s="32"/>
       <c r="N38" s="33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39">
@@ -20338,16 +20338,16 @@
       </c>
       <c r="C39" s="28"/>
       <c r="D39" s="35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H39" s="28"/>
       <c r="I39" s="15"/>
@@ -20383,7 +20383,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>5</v>
@@ -20403,12 +20403,12 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L43" s="10"/>
       <c r="M43" s="11"/>
       <c r="N43" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>20</v>
@@ -20463,7 +20463,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -20483,12 +20483,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49">
@@ -20498,16 +20498,16 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="F49" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>239</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>240</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="15"/>
@@ -20804,10 +20804,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -20821,7 +20821,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -20901,7 +20901,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -20981,7 +20981,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -21061,7 +21061,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -21141,7 +21141,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -21221,7 +21221,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -21301,7 +21301,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -21717,7 +21717,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -21734,7 +21734,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -21759,7 +21759,7 @@
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4">
@@ -21769,13 +21769,13 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>247</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>26</v>
@@ -21814,7 +21814,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -21834,12 +21834,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
@@ -21849,16 +21849,16 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="15"/>
@@ -21894,7 +21894,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -21914,12 +21914,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14">
@@ -21935,10 +21935,10 @@
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="15"/>
@@ -21974,7 +21974,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -21994,12 +21994,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
@@ -22009,13 +22009,13 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>26</v>
@@ -22054,7 +22054,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -22074,12 +22074,12 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
       <c r="N23" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24">
@@ -22089,10 +22089,10 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>14</v>
@@ -22134,7 +22134,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -22154,12 +22154,12 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
       <c r="N28" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29">
@@ -22169,10 +22169,10 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>37</v>
@@ -22214,7 +22214,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -22234,12 +22234,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34">
@@ -22249,10 +22249,10 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>47</v>
@@ -22294,7 +22294,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>5</v>
@@ -22314,12 +22314,12 @@
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L38" s="10"/>
       <c r="M38" s="11"/>
       <c r="N38" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39">
@@ -22335,7 +22335,7 @@
         <v>20</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>20</v>
@@ -22374,7 +22374,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>5</v>
@@ -22394,12 +22394,12 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L43" s="10"/>
       <c r="M43" s="11"/>
       <c r="N43" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44">
@@ -22454,7 +22454,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -22474,12 +22474,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49">
@@ -22495,7 +22495,7 @@
         <v>20</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>20</v>
@@ -22534,7 +22534,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>5</v>
@@ -22554,12 +22554,12 @@
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L53" s="10"/>
       <c r="M53" s="11"/>
       <c r="N53" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54">
@@ -22572,7 +22572,7 @@
         <v>30</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>32</v>
@@ -22614,7 +22614,7 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>5</v>
@@ -22634,12 +22634,12 @@
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L58" s="10"/>
       <c r="M58" s="11"/>
       <c r="N58" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59">
@@ -22649,10 +22649,10 @@
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>47</v>
@@ -22697,7 +22697,7 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>5</v>
@@ -22717,12 +22717,12 @@
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L63" s="10"/>
       <c r="M63" s="11"/>
       <c r="N63" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="64">
@@ -22732,13 +22732,13 @@
       </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E64" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>292</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>293</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>52</v>
@@ -22963,10 +22963,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -22980,7 +22980,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -23000,12 +23000,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
@@ -23015,13 +23015,13 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>26</v>
@@ -23060,7 +23060,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -23080,12 +23080,12 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L8" s="10"/>
       <c r="M8" s="11"/>
       <c r="N8" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9">
@@ -23098,7 +23098,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>43</v>
@@ -23140,7 +23140,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -23160,12 +23160,12 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
       <c r="N13" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14">
@@ -23175,10 +23175,10 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>43</v>
@@ -23220,7 +23220,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -23240,12 +23240,12 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
       <c r="N18" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19">
@@ -23255,16 +23255,16 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>309</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -23300,7 +23300,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -23320,12 +23320,12 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
       <c r="N23" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24">
@@ -23335,16 +23335,16 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>315</v>
-      </c>
       <c r="G24" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="15"/>
@@ -23380,7 +23380,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -23400,12 +23400,12 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
       <c r="N28" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29">
@@ -23421,10 +23421,10 @@
         <v>20</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="15"/>
@@ -23460,7 +23460,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -23480,12 +23480,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34">
@@ -23501,7 +23501,7 @@
         <v>20</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>26</v>
@@ -23540,7 +23540,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>5</v>
@@ -23560,12 +23560,12 @@
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L38" s="10"/>
       <c r="M38" s="11"/>
       <c r="N38" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39">
@@ -23620,7 +23620,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>5</v>
@@ -23640,12 +23640,12 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L43" s="10"/>
       <c r="M43" s="11"/>
       <c r="N43" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44">
@@ -23655,16 +23655,16 @@
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="15"/>
@@ -23700,7 +23700,7 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>5</v>
@@ -23720,12 +23720,12 @@
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L48" s="10"/>
       <c r="M48" s="11"/>
       <c r="N48" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49">
@@ -23735,13 +23735,13 @@
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>26</v>
@@ -23805,7 +23805,7 @@
     </row>
     <row r="56">
       <c r="I56" s="37" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58">
@@ -24046,10 +24046,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="3" t="s">
@@ -24063,7 +24063,7 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
@@ -24083,12 +24083,12 @@
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4">
@@ -24098,16 +24098,16 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="15"/>
@@ -24143,7 +24143,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -24178,16 +24178,16 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>339</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="15"/>
@@ -24223,7 +24223,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>5</v>
@@ -24243,7 +24243,7 @@
       </c>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="11"/>
@@ -24258,13 +24258,13 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>26</v>
@@ -24303,7 +24303,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>5</v>
@@ -24323,7 +24323,7 @@
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L18" s="10"/>
       <c r="M18" s="11"/>
@@ -24338,16 +24338,16 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="15"/>
@@ -24383,7 +24383,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>5</v>
@@ -24403,7 +24403,7 @@
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L23" s="10"/>
       <c r="M23" s="11"/>
@@ -24463,7 +24463,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>5</v>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L28" s="10"/>
       <c r="M28" s="11"/>
@@ -24498,13 +24498,13 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>26</v>
@@ -24543,7 +24543,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>5</v>
@@ -24563,12 +24563,12 @@
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L33" s="10"/>
       <c r="M33" s="11"/>
       <c r="N33" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34">
@@ -24578,13 +24578,13 @@
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>26</v>
